--- a/output/pdf_financials_xlsx/GCOM.xlsx
+++ b/output/pdf_financials_xlsx/GCOM.xlsx
@@ -6810,37 +6810,37 @@
         <v>3.185945</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>3.38641</v>
+        <v>3.185945</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>5.828529</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>12.814523</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>14.413625</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>8.496</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>7.185094</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>7.424765</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>7.53624</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>7.118987</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>7.512348</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>6.582079</v>
       </c>
       <c r="O92" s="3" t="n">
         <v>5.865832</v>
@@ -18158,7 +18158,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -19224,7 +19228,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -21699,7 +21707,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>
@@ -24593,7 +24605,11 @@
           <t>Reserves 5,828,529</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GCOM.xlsx
+++ b/output/pdf_financials_xlsx/GCOM.xlsx
@@ -1200,38 +1200,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D12" s="3" t="n">
+        <v>0.118165</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0.027721</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0.123813</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.087964</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.028299</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.025743</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.005273</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.012962</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.00292</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>0</v>
@@ -2416,22 +2410,22 @@
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-15.091997</v>
+        <v>-15.179961</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-7.432974</v>
+        <v>-7.461273</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-5.761174</v>
+        <v>-5.786917</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-3.170131</v>
+        <v>-3.175404</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-9.065932999999999</v>
+        <v>-9.078894999999999</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.889347</v>
+        <v>-1.892267</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-1.403857</v>
@@ -2562,22 +2556,22 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-15.091997</v>
+        <v>-15.179961</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-7.432974</v>
+        <v>-7.461273</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-5.761174</v>
+        <v>-5.786917</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-3.170131</v>
+        <v>-3.175404</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-8.937716999999999</v>
+        <v>-8.950678999999999</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.877657</v>
+        <v>-1.880577</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-1.394505</v>
@@ -2926,37 +2920,37 @@
         <v>0.136611</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.205703</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.124387</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.06586500000000001</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.094578</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.077098</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.006487</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.79671</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>2.713105</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.271617</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.085433</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>0</v>
+        <v>0.002368</v>
       </c>
     </row>
     <row r="35">
@@ -3058,37 +3052,37 @@
         <v>0.136611</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.205703</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.124387</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.06586500000000001</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.094578</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.077098</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.006487</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.79671</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>2.713105</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.271617</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>0.085433</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>0</v>
+        <v>0.002368</v>
       </c>
     </row>
     <row r="37">
@@ -3850,37 +3844,37 @@
         <v>0.096429</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.278782</v>
+        <v>0.07307900000000001</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.180639</v>
+        <v>0.056252</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.118583</v>
+        <v>0.052718</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.14481</v>
+        <v>0.050232</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.099453</v>
+        <v>0.022355</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.007649</v>
+        <v>0.001162</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>2.90488</v>
+        <v>2.10817</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>5.082321</v>
+        <v>2.369216</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>1.852775</v>
+        <v>1.581158</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>4.255398</v>
+        <v>4.169965</v>
       </c>
       <c r="T48" s="3" t="n">
-        <v>3.577337</v>
+        <v>3.574969</v>
       </c>
     </row>
     <row r="49">
@@ -9775,7 +9769,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -19975,7 +19969,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -53736,7 +53730,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -54826,7 +54820,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
@@ -55936,7 +55930,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
@@ -56483,7 +56477,7 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
@@ -58681,7 +58675,7 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">

--- a/output/pdf_financials_xlsx/GCOM.xlsx
+++ b/output/pdf_financials_xlsx/GCOM.xlsx
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-15.091997</v>
+        <v>-14.88957</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>-7.432974</v>
+        <v>-6.628897</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>-5.761174</v>
+        <v>-5.444811</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-3.170131</v>
+        <v>-3.105151</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>-9.065932999999999</v>
@@ -1584,16 +1584,16 @@
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.202427</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.804077</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.316363</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.06498</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>-0</v>
@@ -1893,11 +1893,15 @@
       <c r="P20" s="3" t="n">
         <v>0.901831</v>
       </c>
-      <c r="Q20" s="3" t="n">
-        <v>-3.120577</v>
-      </c>
-      <c r="R20" s="3" t="n">
-        <v>-3.703859</v>
+      <c r="Q20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="S20" s="3" t="n">
         <v>-0.157542</v>
@@ -1970,10 +1974,10 @@
         <v>0</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>0</v>
+        <v>-1.961159</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>0</v>
+        <v>-1.066078</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>0</v>
@@ -2410,16 +2414,16 @@
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-15.179961</v>
+        <v>-14.977534</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-7.461273</v>
+        <v>-6.657196</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-5.786917</v>
+        <v>-5.470554</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-3.175404</v>
+        <v>-3.110424</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-9.078894999999999</v>
@@ -2556,16 +2560,16 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-15.179961</v>
+        <v>-14.977534</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-7.461273</v>
+        <v>-6.657196</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-5.786917</v>
+        <v>-5.470554</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-3.175404</v>
+        <v>-3.110424</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-8.950678999999999</v>
@@ -2734,16 +2738,16 @@
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-0</v>
+        <v>-1.359522135293363</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>-0</v>
+        <v>-12.12987620715784</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>-0</v>
+        <v>-5.810357788360331</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-0</v>
+        <v>-2.092651854933947</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>-0</v>
@@ -8283,13 +8287,13 @@
         <v>0</v>
       </c>
       <c r="R115" s="3" t="n">
-        <v>0</v>
+        <v>0.582259</v>
       </c>
       <c r="S115" s="3" t="n">
-        <v>0</v>
+        <v>0.409952</v>
       </c>
       <c r="T115" s="3" t="n">
-        <v>0</v>
+        <v>0.606862</v>
       </c>
     </row>
     <row r="116">
@@ -29904,7 +29908,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>
@@ -41676,7 +41684,11 @@
           <t>Deferred income tax recovery (note 12)</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr"/>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E295" t="inlineStr">
         <is>
           <t>-</t>
@@ -43206,7 +43218,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr"/>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E309" t="inlineStr">
         <is>
           <t>-</t>
@@ -51092,7 +51108,11 @@
           <t>Common shares issued for cash</t>
         </is>
       </c>
-      <c r="D381" t="inlineStr"/>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E381" s="5" t="n">
         <v>32.65375</v>
       </c>
@@ -53179,7 +53199,11 @@
           <t>Loss from discontinued operation\ (note 14)</t>
         </is>
       </c>
-      <c r="D400" t="inlineStr"/>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E400" t="inlineStr">
         <is>
           <t>-</t>
@@ -58350,7 +58374,11 @@
           <t>Deferred income tax recovery (note 12)</t>
         </is>
       </c>
-      <c r="D447" t="inlineStr"/>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E447" t="inlineStr">
         <is>
           <t>-</t>
@@ -59759,7 +59787,11 @@
           <t>Deferred income tax recovery (note 11)</t>
         </is>
       </c>
-      <c r="D460" t="inlineStr"/>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E460" t="inlineStr">
         <is>
           <t>-</t>
@@ -62185,7 +62217,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D482" t="inlineStr"/>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E482" t="inlineStr">
         <is>
           <t>-</t>
